--- a/DATA/demand/generated_random_demand_scenarios.xlsx
+++ b/DATA/demand/generated_random_demand_scenarios.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/DATA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/DATA/demand/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="89" documentId="4_{2D12AA8F-2E40-44A7-809E-99A656943D37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B3B9901-D6A6-4F41-985E-EA7BE291393B}"/>
+  <xr:revisionPtr revIDLastSave="92" documentId="4_{2D12AA8F-2E40-44A7-809E-99A656943D37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96DA80F2-581F-40C0-87FD-A3C59C4F2243}"/>
   <bookViews>
-    <workbookView xWindow="13550" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="37" activeTab="49" xr2:uid="{52D9C27D-0EF6-DD41-9728-0267E68F7539}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{52D9C27D-0EF6-DD41-9728-0267E68F7539}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenario_1" sheetId="1" r:id="rId1"/>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1150" uniqueCount="23">
   <si>
     <t>Vaccine</t>
   </si>
@@ -155,15 +155,6 @@
   <si>
     <t>PCV</t>
   </si>
-  <si>
-    <t>Demand</t>
-  </si>
-  <si>
-    <t>Capacity</t>
-  </si>
-  <si>
-    <t>Scaled Capacity</t>
-  </si>
 </sst>
 </file>
 
@@ -225,1186 +216,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Updated Demand v Capacity - Antigen</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Scenario_50!$G$28</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Demand</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>Scenario_50!$F$29:$F$40</c:f>
-              <c:strCache>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>Measles</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Mumps</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Rubella</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Diphtheria</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Tetanus</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Pertussis</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Hepatitis_B</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Hib</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Polio</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>HPV</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Rotavirus</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>PCV</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Scenario_50!$G$29:$G$40</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>392433645.50669652</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>26202387.718242884</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>378800029.55425608</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>707933804.44231188</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>606585491.26533163</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>333801996.37829506</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>393195221.63544863</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>300189881.13855594</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>651240059.78908348</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>29003959.642525043</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>190555609.21358225</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>223612967.86375159</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-9E7F-4022-B766-74C9B2DA4614}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Scenario_50!$H$28</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Capacity</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>Scenario_50!$F$29:$F$40</c:f>
-              <c:strCache>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>Measles</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Mumps</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Rubella</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Diphtheria</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Tetanus</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Pertussis</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Hepatitis_B</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Hib</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Polio</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>HPV</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Rotavirus</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>PCV</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Scenario_50!$H$29:$H$40</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>264193987.60999981</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>23500755.779999979</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>225259255.1799998</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>450649755.54799962</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>462199401.72799963</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>260776685.13600001</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>203995434.479</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>200773991.76300001</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>435182360.99999928</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>64210185.419999987</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>138970173.69999999</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>148936259.0999997</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-9E7F-4022-B766-74C9B2DA4614}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Scenario_50!$I$28</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Scaled Capacity</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent3"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:val>
-            <c:numRef>
-              <c:f>Scenario_50!$I$29:$I$40</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>369871582.65399969</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>32901058.091999967</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>315362957.25199968</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>630909657.7671994</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>647079162.41919947</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>365087359.1904</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>285593608.27059996</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>281083588.46820003</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>609255305.3999989</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>89894259.58799997</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>194558243.17999998</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>208510762.73999956</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-9E7F-4022-B766-74C9B2DA4614}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
-        <c:axId val="268553471"/>
-        <c:axId val="278034783"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="268553471"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="278034783"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="278034783"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="0.00E+00" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="268553471"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>749299</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>739774</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C14EA4F2-733E-B905-0212-2D6BC9B78C2D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -23091,204 +21902,46 @@
         <v>571232114.87386942</v>
       </c>
     </row>
-    <row r="28" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F28" t="s">
-        <v>0</v>
-      </c>
-      <c r="G28" t="s">
-        <v>23</v>
-      </c>
-      <c r="H28" t="s">
-        <v>24</v>
-      </c>
-      <c r="I28" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="29" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F29" t="s">
-        <v>11</v>
-      </c>
-      <c r="G29">
-        <v>392433645.50669652</v>
-      </c>
-      <c r="H29" s="1">
-        <v>264193987.60999981</v>
-      </c>
-      <c r="I29">
-        <f>H29*1.4</f>
-        <v>369871582.65399969</v>
-      </c>
-    </row>
-    <row r="30" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F30" t="s">
-        <v>12</v>
-      </c>
-      <c r="G30">
-        <v>26202387.718242884</v>
-      </c>
-      <c r="H30" s="1">
-        <v>23500755.779999979</v>
-      </c>
-      <c r="I30">
-        <f t="shared" ref="I30:I40" si="0">H30*1.4</f>
-        <v>32901058.091999967</v>
-      </c>
-    </row>
-    <row r="31" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F31" t="s">
-        <v>13</v>
-      </c>
-      <c r="G31">
-        <v>378800029.55425608</v>
-      </c>
-      <c r="H31" s="1">
-        <v>225259255.1799998</v>
-      </c>
-      <c r="I31">
-        <f t="shared" si="0"/>
-        <v>315362957.25199968</v>
-      </c>
-    </row>
-    <row r="32" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F32" t="s">
-        <v>14</v>
-      </c>
-      <c r="G32">
-        <v>707933804.44231188</v>
-      </c>
-      <c r="H32" s="1">
-        <v>450649755.54799962</v>
-      </c>
-      <c r="I32">
-        <f t="shared" si="0"/>
-        <v>630909657.7671994</v>
-      </c>
-    </row>
-    <row r="33" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F33" t="s">
-        <v>15</v>
-      </c>
-      <c r="G33">
-        <v>606585491.26533163</v>
-      </c>
-      <c r="H33" s="1">
-        <v>462199401.72799963</v>
-      </c>
-      <c r="I33">
-        <f t="shared" si="0"/>
-        <v>647079162.41919947</v>
-      </c>
-    </row>
-    <row r="34" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F34" t="s">
-        <v>16</v>
-      </c>
-      <c r="G34">
-        <v>333801996.37829506</v>
-      </c>
-      <c r="H34" s="1">
-        <v>260776685.13600001</v>
-      </c>
-      <c r="I34">
-        <f t="shared" si="0"/>
-        <v>365087359.1904</v>
-      </c>
-    </row>
-    <row r="35" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F35" t="s">
-        <v>17</v>
-      </c>
-      <c r="G35">
-        <v>393195221.63544863</v>
-      </c>
-      <c r="H35" s="1">
-        <v>203995434.479</v>
-      </c>
-      <c r="I35">
-        <f t="shared" si="0"/>
-        <v>285593608.27059996</v>
-      </c>
-    </row>
-    <row r="36" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F36" t="s">
-        <v>18</v>
-      </c>
-      <c r="G36">
-        <v>300189881.13855594</v>
-      </c>
-      <c r="H36" s="1">
-        <v>200773991.76300001</v>
-      </c>
-      <c r="I36">
-        <f t="shared" si="0"/>
-        <v>281083588.46820003</v>
-      </c>
-    </row>
-    <row r="37" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F37" t="s">
-        <v>19</v>
-      </c>
-      <c r="G37">
-        <v>651240059.78908348</v>
-      </c>
-      <c r="H37" s="1">
-        <v>435182360.99999928</v>
-      </c>
-      <c r="I37">
-        <f t="shared" si="0"/>
-        <v>609255305.3999989</v>
-      </c>
-    </row>
-    <row r="38" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F38" t="s">
-        <v>20</v>
-      </c>
-      <c r="G38">
-        <v>29003959.642525043</v>
-      </c>
-      <c r="H38" s="1">
-        <v>64210185.419999987</v>
-      </c>
-      <c r="I38">
-        <f t="shared" si="0"/>
-        <v>89894259.58799997</v>
-      </c>
-    </row>
-    <row r="39" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F39" t="s">
-        <v>21</v>
-      </c>
-      <c r="G39">
-        <v>190555609.21358225</v>
-      </c>
-      <c r="H39" s="1">
-        <v>138970173.69999999</v>
-      </c>
-      <c r="I39">
-        <f t="shared" si="0"/>
-        <v>194558243.17999998</v>
-      </c>
-    </row>
-    <row r="40" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F40" t="s">
-        <v>22</v>
-      </c>
-      <c r="G40">
-        <v>223612967.86375159</v>
-      </c>
-      <c r="H40" s="1">
-        <v>148936259.0999997</v>
-      </c>
-      <c r="I40">
-        <f t="shared" si="0"/>
-        <v>208510762.73999956</v>
-      </c>
-    </row>
-    <row r="47" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H29" s="1"/>
+    </row>
+    <row r="30" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H30" s="1"/>
+    </row>
+    <row r="31" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H31" s="1"/>
+    </row>
+    <row r="32" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H32" s="1"/>
+    </row>
+    <row r="33" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="H33" s="1"/>
+    </row>
+    <row r="34" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="H34" s="1"/>
+    </row>
+    <row r="35" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="H35" s="1"/>
+    </row>
+    <row r="36" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="H36" s="1"/>
+    </row>
+    <row r="37" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="H37" s="1"/>
+    </row>
+    <row r="38" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="H38" s="1"/>
+    </row>
+    <row r="39" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="H39" s="1"/>
+    </row>
+    <row r="40" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="H40" s="1"/>
+    </row>
+    <row r="47" spans="6:8" x14ac:dyDescent="0.25">
       <c r="F47" s="1"/>
     </row>
-    <row r="48" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="6:8" x14ac:dyDescent="0.25">
       <c r="F48" s="1"/>
     </row>
     <row r="49" spans="6:6" x14ac:dyDescent="0.25">
@@ -23323,7 +21976,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
